--- a/output/pdf_financials_xlsx/BG.xlsx
+++ b/output/pdf_financials_xlsx/BG.xlsx
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.138962</v>
+        <v>0.666955</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.14053</v>
+        <v>0.775087</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.175904</v>
+        <v>0.845601</v>
       </c>
     </row>
     <row r="93">
@@ -3062,7 +3062,11 @@
           <t>Warrant reserve 9</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.236971</v>
       </c>
@@ -3089,7 +3093,11 @@
           <t>Share based payments reserve 10</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
         <v>0.291022</v>
       </c>

--- a/output/pdf_financials_xlsx/BG.xlsx
+++ b/output/pdf_financials_xlsx/BG.xlsx
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.293786</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.026565</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.036118</v>
       </c>
     </row>
     <row r="35">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.293786</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.026565</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.036118</v>
       </c>
     </row>
     <row r="37">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">

--- a/output/pdf_financials_xlsx/BG.xlsx
+++ b/output/pdf_financials_xlsx/BG.xlsx
@@ -1621,10 +1621,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.188681</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.331228</v>
       </c>
     </row>
     <row r="65">
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0258</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>0</v>
